--- a/.claude/skills/mice-estimate/assets/remember_template.xlsx
+++ b/.claude/skills/mice-estimate/assets/remember_template.xlsx
@@ -2635,7 +2635,7 @@
       </c>
       <c r="B11" s="109" t="inlineStr">
         <is>
-          <t>센드버드코리아 컨퍼런스 (7월)</t>
+          <t>(외부 주입 - 행사명)</t>
         </is>
       </c>
       <c r="C11" s="110" t="n"/>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="B13" s="109" t="inlineStr">
         <is>
-          <t>소피텔 앰배서더 서울</t>
+          <t>(외부 주입 - 베뉴)</t>
         </is>
       </c>
       <c r="C13" s="110" t="n"/>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="B14" s="109" t="inlineStr">
         <is>
-          <t>7월 9일 1일 full day 기준(9 to 18) / 240명 규모</t>
+          <t>(외부 주입 - 일시·규모)</t>
         </is>
       </c>
       <c r="C14" s="110" t="n"/>
@@ -2809,8 +2809,10 @@
           <t>견적일시</t>
         </is>
       </c>
-      <c r="B15" s="163" t="n">
-        <v>46095</v>
+      <c r="B15" s="163" t="inlineStr">
+        <is>
+          <t>(외부 주입 - 견적일시)</t>
+        </is>
       </c>
       <c r="C15" s="164" t="n"/>
       <c r="D15" s="88" t="n"/>
@@ -2887,8 +2889,9 @@
           <t>정가</t>
         </is>
       </c>
-      <c r="B17" s="165" t="n">
-        <v>48370000</v>
+      <c r="B17" s="165">
+        <f>F25+F35+F43+F50+F57+F64+F70</f>
+        <v/>
       </c>
       <c r="C17" s="162" t="n"/>
       <c r="D17" s="88" t="n"/>
@@ -2955,8 +2958,9 @@
           <t>최종 견적</t>
         </is>
       </c>
-      <c r="B19" s="167" t="n">
-        <v>42370000</v>
+      <c r="B19" s="167">
+        <f>B17+B18</f>
+        <v/>
       </c>
       <c r="C19" s="162" t="n"/>
       <c r="D19" s="88" t="n"/>
@@ -3148,12 +3152,12 @@
       </c>
       <c r="B24" s="30" t="inlineStr">
         <is>
-          <t>소피텔 앰배서더 서울</t>
+          <t>(외부 주입 - 베뉴)</t>
         </is>
       </c>
       <c r="C24" s="31" t="inlineStr">
         <is>
-          <t>(서울송파) 잠실역 / Grand Ballroom / max 300명(연회식)</t>
+          <t>(외부 주입 - 지역 / 홀 / 수용 인원)</t>
         </is>
       </c>
       <c r="D24" s="170" t="n">
@@ -4583,7 +4587,7 @@
     <row r="59" ht="29.25" customHeight="1" s="133">
       <c r="A59" s="116" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6. PCO 이윤</t>
+          <t xml:space="preserve">  6. PCO 기획료</t>
         </is>
       </c>
       <c r="B59" s="117" t="n"/>
@@ -4594,8 +4598,9 @@
         </is>
       </c>
       <c r="E59" s="145" t="n"/>
-      <c r="F59" s="169" t="n">
-        <v>8870000</v>
+      <c r="F59" s="169">
+        <f>F64</f>
+        <v/>
       </c>
       <c r="G59" s="19" t="inlineStr">
         <is>
@@ -4640,7 +4645,7 @@
       </c>
       <c r="D60" s="24" t="inlineStr">
         <is>
-          <t>운영비 합계</t>
+          <t>직접비 합계</t>
         </is>
       </c>
       <c r="E60" s="57" t="inlineStr">
@@ -4681,31 +4686,33 @@
     <row r="61" ht="29.25" customHeight="1" s="133">
       <c r="A61" s="200" t="inlineStr">
         <is>
-          <t>인건비</t>
+          <t>PCO 기획료</t>
         </is>
       </c>
       <c r="B61" s="201" t="inlineStr">
         <is>
-          <t>운영비의 15%</t>
+          <t>직접비의 25%</t>
         </is>
       </c>
       <c r="C61" s="202" t="inlineStr">
         <is>
-          <t>행사총괄PM 1인 / 실무PM 2인 / 운영담당 3인</t>
+          <t>행사 기획·운영 총괄(PM·실무·운영담당) 및 일반관리 포함</t>
         </is>
       </c>
-      <c r="D61" s="195" t="n">
-        <v>33500000</v>
+      <c r="D61" s="195">
+        <f>F25+F35+F43+F50+F57+F68</f>
+        <v/>
       </c>
       <c r="E61" s="98" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
-      <c r="F61" s="203" t="n">
-        <v>5020000</v>
+      <c r="F61" s="203">
+        <f>FLOOR(D61*E61,10000)</f>
+        <v/>
       </c>
       <c r="G61" s="185" t="inlineStr">
         <is>
-          <t>모객비용 제외 운영비 합산 기준</t>
+          <t>쇼업 보장 제외 직접비 합산 · 만원 미만 절사</t>
         </is>
       </c>
       <c r="H61" s="115" t="n"/>
@@ -4729,30 +4736,12 @@
       <c r="Z61" s="186" t="n"/>
     </row>
     <row r="62" ht="29.25" customHeight="1" s="133">
-      <c r="A62" s="204" t="inlineStr">
-        <is>
-          <t>기업이윤+관리비</t>
-        </is>
-      </c>
-      <c r="B62" s="205" t="inlineStr">
-        <is>
-          <t>(운영비+인건비)의 10%</t>
-        </is>
-      </c>
-      <c r="C62" s="206" t="inlineStr">
-        <is>
-          <t>기업이윤 및 일반관리비 통합</t>
-        </is>
-      </c>
-      <c r="D62" s="207" t="n">
-        <v>38520000</v>
-      </c>
-      <c r="E62" s="99" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F62" s="208" t="n">
-        <v>3850000</v>
-      </c>
+      <c r="A62" s="204" t="n"/>
+      <c r="B62" s="205" t="n"/>
+      <c r="C62" s="206" t="n"/>
+      <c r="D62" s="207" t="n"/>
+      <c r="E62" s="99" t="n"/>
+      <c r="F62" s="208" t="n"/>
       <c r="G62" s="209" t="n"/>
       <c r="H62" s="115" t="n"/>
       <c r="I62" s="186" t="n"/>
@@ -4812,8 +4801,9 @@
       <c r="C64" s="135" t="n"/>
       <c r="D64" s="175" t="n"/>
       <c r="E64" s="212" t="n"/>
-      <c r="F64" s="213" t="n">
-        <v>8870000</v>
+      <c r="F64" s="213">
+        <f>F61</f>
+        <v/>
       </c>
       <c r="G64" s="189" t="n"/>
       <c r="H64" s="123" t="n"/>
@@ -30915,13 +30905,13 @@
     <mergeCell ref="A54:A55"/>
     <mergeCell ref="G61:H61"/>
     <mergeCell ref="E29:E32"/>
-    <mergeCell ref="G23:H23"/>
     <mergeCell ref="A50:C50"/>
     <mergeCell ref="G70:H70"/>
+    <mergeCell ref="G23:H23"/>
     <mergeCell ref="E39:E42"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="D22:E22"/>
     <mergeCell ref="A57:C57"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G48:H48"/>
     <mergeCell ref="D45:E45"/>
     <mergeCell ref="G39:H39"/>
     <mergeCell ref="B21:C21"/>
@@ -31294,7 +31284,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>센드버드코리아 컨퍼런스 (7월)</t>
+          <t>(외부 주입 - 행사명)</t>
         </is>
       </c>
       <c r="C11" s="7" t="n"/>
@@ -31382,7 +31372,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>소피텔 앰배서더 서울 (또는 별도 행사장)</t>
+          <t>(외부 주입 - 베뉴)</t>
         </is>
       </c>
       <c r="C13" s="7" t="n"/>
@@ -31426,7 +31416,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>7월 9일 1일 full day 기준(9 to 18) / 350명 규모</t>
+          <t>(외부 주입 - 일시·규모)</t>
         </is>
       </c>
       <c r="C14" s="7" t="n"/>
@@ -31468,8 +31458,10 @@
           <t>견적일시</t>
         </is>
       </c>
-      <c r="B15" s="218" t="n">
-        <v>46095</v>
+      <c r="B15" s="218" t="inlineStr">
+        <is>
+          <t>(외부 주입 - 견적일시)</t>
+        </is>
       </c>
       <c r="C15" s="219" t="n"/>
       <c r="D15" s="88" t="n"/>
@@ -31546,8 +31538,9 @@
           <t>정가</t>
         </is>
       </c>
-      <c r="B17" s="220" t="n">
-        <v>55960000</v>
+      <c r="B17" s="220">
+        <f>F25+F35+F43+F50+F57+F64+F70</f>
+        <v/>
       </c>
       <c r="C17" s="162" t="n"/>
       <c r="D17" s="88" t="n"/>
@@ -31614,8 +31607,9 @@
           <t>최종 견적</t>
         </is>
       </c>
-      <c r="B19" s="167" t="n">
-        <v>49960000</v>
+      <c r="B19" s="167">
+        <f>B17+B18</f>
+        <v/>
       </c>
       <c r="C19" s="162" t="n"/>
       <c r="D19" s="88" t="n"/>
@@ -31806,12 +31800,12 @@
       </c>
       <c r="B24" s="30" t="inlineStr">
         <is>
-          <t>소피텔 앰배서더 서울</t>
+          <t>(외부 주입 - 베뉴)</t>
         </is>
       </c>
       <c r="C24" s="31" t="inlineStr">
         <is>
-          <t>(서울송파) Grand Ballroom max 300명(연회식) → 350명 시 별도 행사장 검토</t>
+          <t>(외부 주입 - 지역 / 홀 / 수용 인원)</t>
         </is>
       </c>
       <c r="D24" s="170" t="n">
@@ -31825,7 +31819,7 @@
       </c>
       <c r="G24" s="173" t="inlineStr">
         <is>
-          <t>* 소피텔 max 300명 → 350명 규모 시 별도 행사장 협의 필요</t>
+          <t>베뉴 비용 별도 (수용 인원 초과 시 별도 행사장 협의)</t>
         </is>
       </c>
       <c r="H24" s="174" t="n"/>
@@ -33248,8 +33242,9 @@
         </is>
       </c>
       <c r="E59" s="145" t="n"/>
-      <c r="F59" s="169" t="n">
-        <v>10460000</v>
+      <c r="F59" s="169">
+        <f>F64</f>
+        <v/>
       </c>
       <c r="G59" s="19" t="inlineStr">
         <is>
@@ -33294,7 +33289,7 @@
       </c>
       <c r="D60" s="24" t="inlineStr">
         <is>
-          <t>운영비 합계</t>
+          <t>직접비 합계</t>
         </is>
       </c>
       <c r="E60" s="57" t="inlineStr">
@@ -33335,31 +33330,33 @@
     <row r="61" ht="29.25" customHeight="1" s="133">
       <c r="A61" s="200" t="inlineStr">
         <is>
-          <t>인건비</t>
+          <t>PCO 기획료</t>
         </is>
       </c>
       <c r="B61" s="201" t="inlineStr">
         <is>
-          <t>운영비의 15%</t>
+          <t>직접비의 25%</t>
         </is>
       </c>
       <c r="C61" s="202" t="inlineStr">
         <is>
-          <t>행사총괄PM 1인 / 실무PM 2인 / 운영담당 3인</t>
+          <t>행사 기획·운영 총괄(PM·실무·운영담당) 및 일반관리 포함</t>
         </is>
       </c>
-      <c r="D61" s="195" t="n">
-        <v>39500000</v>
+      <c r="D61" s="195">
+        <f>F25+F35+F43+F50+F57+F68</f>
+        <v/>
       </c>
       <c r="E61" s="98" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
-      <c r="F61" s="203" t="n">
-        <v>5920000</v>
+      <c r="F61" s="203">
+        <f>FLOOR(D61*E61,10000)</f>
+        <v/>
       </c>
       <c r="G61" s="185" t="inlineStr">
         <is>
-          <t>모객비용 제외 운영비 합산 기준</t>
+          <t>쇼업 보장 제외 직접비 합산 · 만원 미만 절사</t>
         </is>
       </c>
       <c r="H61" s="115" t="n"/>
@@ -33383,30 +33380,12 @@
       <c r="Z61" s="186" t="n"/>
     </row>
     <row r="62" ht="29.25" customHeight="1" s="133">
-      <c r="A62" s="204" t="inlineStr">
-        <is>
-          <t>기업이윤+관리비</t>
-        </is>
-      </c>
-      <c r="B62" s="205" t="inlineStr">
-        <is>
-          <t>(운영비+인건비)의 10%</t>
-        </is>
-      </c>
-      <c r="C62" s="206" t="inlineStr">
-        <is>
-          <t>기업이윤 및 일반관리비 통합</t>
-        </is>
-      </c>
-      <c r="D62" s="207" t="n">
-        <v>45420000</v>
-      </c>
-      <c r="E62" s="99" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F62" s="208" t="n">
-        <v>4540000</v>
-      </c>
+      <c r="A62" s="204" t="n"/>
+      <c r="B62" s="205" t="n"/>
+      <c r="C62" s="206" t="n"/>
+      <c r="D62" s="207" t="n"/>
+      <c r="E62" s="99" t="n"/>
+      <c r="F62" s="208" t="n"/>
       <c r="G62" s="209" t="n"/>
       <c r="H62" s="115" t="n"/>
       <c r="I62" s="186" t="n"/>
@@ -33466,8 +33445,9 @@
       <c r="C64" s="135" t="n"/>
       <c r="D64" s="175" t="n"/>
       <c r="E64" s="212" t="n"/>
-      <c r="F64" s="213" t="n">
-        <v>10460000</v>
+      <c r="F64" s="213">
+        <f>F61</f>
+        <v/>
       </c>
       <c r="G64" s="189" t="n"/>
       <c r="H64" s="123" t="n"/>
@@ -59565,15 +59545,15 @@
     <mergeCell ref="G42:H42"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="G67:H67"/>
+    <mergeCell ref="A54:A55"/>
     <mergeCell ref="G61:H61"/>
+    <mergeCell ref="E29:E32"/>
     <mergeCell ref="G23:H23"/>
-    <mergeCell ref="E29:E32"/>
     <mergeCell ref="A50:C50"/>
     <mergeCell ref="G70:H70"/>
-    <mergeCell ref="D22:E22"/>
     <mergeCell ref="E39:E42"/>
     <mergeCell ref="G48:H48"/>
-    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="D22:E22"/>
     <mergeCell ref="A57:C57"/>
     <mergeCell ref="D45:E45"/>
     <mergeCell ref="G39:H39"/>
